--- a/currentbuild/StructureDefinition-AuditEventNorwayTokenProfile.xlsx
+++ b/currentbuild/StructureDefinition-AuditEventNorwayTokenProfile.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-12T11:23:40+00:00</t>
+    <t>2023-02-13T09:41:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/StructureDefinition-AuditEventNorwayTokenProfile.xlsx
+++ b/currentbuild/StructureDefinition-AuditEventNorwayTokenProfile.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-08T20:17:08+00:00</t>
+    <t>2024-01-12T06:32:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/StructureDefinition-AuditEventNorwayTokenProfile.xlsx
+++ b/currentbuild/StructureDefinition-AuditEventNorwayTokenProfile.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>0.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -45,7 +45,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>National profile for AuditEvent for security token mapping</t>
+    <t>Audit from a API service organization perspective</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-12T06:32:37+00:00</t>
+    <t>2024-01-12T06:41:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/StructureDefinition-AuditEventNorwayTokenProfile.xlsx
+++ b/currentbuild/StructureDefinition-AuditEventNorwayTokenProfile.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.0</t>
+    <t>0.3.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-12T06:41:33+00:00</t>
+    <t>2024-01-12T11:46:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/StructureDefinition-AuditEventNorwayTokenProfile.xlsx
+++ b/currentbuild/StructureDefinition-AuditEventNorwayTokenProfile.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-12T11:46:53+00:00</t>
+    <t>2024-01-12T11:54:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
